--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N92_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N92_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>77.91919431167109</v>
+        <v>12.66186907564655</v>
       </c>
       <c r="D2" t="n">
-        <v>26.29564652327639</v>
+        <v>4.273042560032414</v>
       </c>
       <c r="E2" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F2" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.48469754156156</v>
+        <v>11.94126335050375</v>
       </c>
       <c r="D3" t="n">
-        <v>71.31191764008082</v>
+        <v>11.58818661651313</v>
       </c>
       <c r="E3" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F3" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.46554991662567</v>
+        <v>9.175651861451671</v>
       </c>
       <c r="D4" t="n">
-        <v>33.43853138137217</v>
+        <v>5.433761349472977</v>
       </c>
       <c r="E4" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F4" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.58347874759716</v>
+        <v>10.00731529648454</v>
       </c>
       <c r="D5" t="n">
-        <v>61.69869809839987</v>
+        <v>10.02603844098998</v>
       </c>
       <c r="E5" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F5" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>68.89903776911571</v>
+        <v>11.1960936374813</v>
       </c>
       <c r="D6" t="n">
-        <v>7.204269724793327</v>
+        <v>1.170693830278916</v>
       </c>
       <c r="E6" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F6" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.55584646125919</v>
+        <v>9.515325049954619</v>
       </c>
       <c r="D7" t="n">
-        <v>58.52995482623188</v>
+        <v>9.51111765926268</v>
       </c>
       <c r="E7" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F7" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.35194320020582</v>
+        <v>7.694690770033446</v>
       </c>
       <c r="D8" t="n">
-        <v>47.48836998806084</v>
+        <v>7.716860123059886</v>
       </c>
       <c r="E8" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F8" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.2937177779453</v>
+        <v>8.010229138916111</v>
       </c>
       <c r="D9" t="n">
-        <v>49.24299015749064</v>
+        <v>8.00198590059223</v>
       </c>
       <c r="E9" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F9" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>82.5689486461542</v>
+        <v>13.41745415500006</v>
       </c>
       <c r="D10" t="n">
-        <v>82.01255487850474</v>
+        <v>13.32704016775702</v>
       </c>
       <c r="E10" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F10" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>83.8762142544915</v>
+        <v>13.62988481635487</v>
       </c>
       <c r="D11" t="n">
-        <v>83.22494611092944</v>
+        <v>13.52405374302603</v>
       </c>
       <c r="E11" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F11" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.29766657298644</v>
+        <v>8.498370818110295</v>
       </c>
       <c r="D12" t="n">
-        <v>45.5411901469428</v>
+        <v>7.400443398878206</v>
       </c>
       <c r="E12" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F12" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>46.04896011757388</v>
+        <v>7.482956019105755</v>
       </c>
       <c r="D13" t="n">
-        <v>45.58173477465152</v>
+        <v>7.407031900880871</v>
       </c>
       <c r="E13" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F13" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>62.89656092646877</v>
+        <v>10.22069115055118</v>
       </c>
       <c r="D14" t="n">
-        <v>62.87869206291051</v>
+        <v>10.21778746022296</v>
       </c>
       <c r="E14" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F14" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>55.01897593979146</v>
+        <v>8.940583590216113</v>
       </c>
       <c r="D15" t="n">
-        <v>54.51966882914368</v>
+        <v>8.859446184735848</v>
       </c>
       <c r="E15" t="n">
-        <v>12.38225191227517</v>
+        <v>2.012115935744715</v>
       </c>
       <c r="F15" t="n">
-        <v>20.0584843572228</v>
+        <v>3.259503708048705</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
